--- a/plantillas/comparativo_marco_legal.xlsx
+++ b/plantillas/comparativo_marco_legal.xlsx
@@ -14,9 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-defensoras" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hn" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="definiciones" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indicadores" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="instrucciones" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="co" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="definiciones" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="indicadores" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="instrucciones" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1894,6 +1895,892 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>es_subindicador</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>i01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>1. Definición amplia e inclusiva de persona defensora</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>i01a</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Personas físicas que actúan individualmente</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>i01b</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Integrantes de grupos, organizaciones o movimientos sociales</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>i01c</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Personas morales y organizaciones como sujetos protegidos</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>i01d</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Comunidades, pueblos o colectivos sin personalidad jurídica, nombrados expresamente</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>i01e</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>No exige registro, acreditación ni pertenencia a organización</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>i01f</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Reconoce la defensa como actividad ocasional o no profesional</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>i02</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2. Definición amplia e inclusiva de persona periodista</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>i02a</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Personas físicas, además de medios</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>i02b</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Medios de toda índole (públicos, comunitarios, privados, independientes, universitarios, experimentales u otros)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>i02c</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Criterio funcional: se es periodista por la actividad de informar, no por título, credencial o relación laboral</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>i02d</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>No exige acreditación ni personalidad jurídica</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>i02e</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Nombra expresamente a colaboradores, columnistas o auxiliares</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>i02f</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Incluye medios y entornos digitales</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>i02g</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Define el periodismo como actividad de interés público, además de definir al periodista</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>i03</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>3. Concepto amplio y adecuado de agresión</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>i03a</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Vida</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>i03b</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Integridad física</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>i03c</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Integridad psicológica</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>i03d</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Integridad moral</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>i03e</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Integridad económica</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>i03f</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Libertad y seguridad</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>i03g</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Bienes</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>i03h</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Derechos</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>i03i</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Entorno familiar, laboral u organizativo</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>i03j</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Ámbito digital (campañas, ataques informáticos, revelación de datos)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>i03k</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Acoso judicial (citatorios, demandas para hostigar)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>i03l</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Violencia y acoso sexual</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>i04</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>4. Perspectiva de género y enfoques diferenciados</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>i05</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>5. Enfoque individual y colectivo de la protección</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>i06</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>6. Medidas diversas de protección</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>i06a</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Medidas urgentes de protección</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>i06b</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Medidas preventivas</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>i06c</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Medidas de protección</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>i06d</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Medidas de prevención (política pública)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>i06e</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Medidas de carácter social (atención, apoyo económico, psicológico, retorno)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>i07</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>7. Participación de sociedad civil, periodistas y personas defensoras con voz y voto en un Consejo Consultivo</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>i08</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>8. Junta de Gobierno o Consejo de Medidas interinstitucional con instituciones clave</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>i09</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>9. Obligación legal de cooperación de autoridades locales y cuerpos de seguridad</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>i10</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>10. Pasos definidos para acceder al mecanismo</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>i11</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>11. Áreas técnicas diferenciadas (análisis de riesgo, implementación, prevención, monitoreo y seguimiento)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>i12</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>12. Tiempos establecidos para cada procedimiento</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>i13</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>13. Sistemas de alerta temprana y planes de contingencia</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>i14</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>14. Recursos de inconformidad</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>i15</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>15. Posibilidad de firmar convenios de colaboración</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>i16</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>16. Mesa de trabajo multisectorial</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>i17</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>17. Mecanismos para obtener recursos financieros (fondo, fideicomiso, presupuesto garantizado)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>i18</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>18. Responsabilidades o sanciones para servidores públicos</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>i19</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>19. Obligación de emitir informes periódicos públicos</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>i20</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>20. Unidades y mecanismos claros de transparencia y acceso a la información</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1934,7 +2821,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Para agregar un estado: copia la hoja de un estado, renómbrala con su clave INEGI (por ejemplo 14 para Jalisco) y llena los metadatos y las celdas. Si el estado tiene más de una ley, usa la clave con un sufijo (05-periodistas, 05-defensoras). La hoja 'hn' es la ley nacional de Honduras.</t>
+          <t>Para agregar un estado: copia la hoja de un estado, renómbrala con su clave INEGI (por ejemplo 14 para Jalisco) y llena los metadatos y las celdas. Si el estado tiene más de una ley, usa la clave con un sufijo (05-periodistas, 05-defensoras). Las hojas 'hn' y 'co' son las normas nacionales de Honduras y Colombia.</t>
         </is>
       </c>
     </row>
@@ -10555,7 +11442,1444 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>cve_ent</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>pais</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>corto</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Decreto 4912 de 2011, Programa de Prevención y Protección de los derechos a la vida, la libertad, la integridad y la seguridad de personas, grupos y comunidades (Colombia)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>publicacion</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Diario Oficial 48.294, 26 de diciembre de 2011; compilado en el Decreto Único Reglamentario 1066 de 2015 (arts. 2.4.1.2.1 y ss.)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ultima_reforma</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Decreto 1225 de 2012 (texto codificado); desarrollos posteriores por Decretos 1314 de 2016 y 2078 de 2017</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>organo</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Unidad Nacional de Protección (UNP), con el Cerrem, el Grupo de Valoración Preliminar y el Ctrai; Ministerio del Interior y Policía Nacional</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>https://normativa.colpensiones.gov.co/colpens/docs/decreto_4912_2011.htm</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>indicador</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>articulos</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>i01</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1. Definición amplia e inclusiva de persona defensora</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 3 num. 1 y 5, 6 num. 2, 5 y 9</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>No define a la persona defensora; protege a 'dirigentes, representantes o activistas de organizaciones defensoras de derechos humanos, de víctimas, sociales, cívicas, comunales o campesinas', a miembros de grupos étnicos y a reclamantes de tierras. El activista debe acreditarse con certificación de su organización o de una autoridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>i01a</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Personas físicas que actúan individualmente</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 3 num. 1, 6 num. 2</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>La persona individual entra como activista, pero acreditada por una organización</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>i01b</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Integrantes de grupos, organizaciones o movimientos sociales</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Art. 6 num. 2</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>i01c</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Personas morales y organizaciones como sujetos protegidos</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 1, 11 lit. g</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Protege 'grupos y comunidades' y blinda sedes de organizaciones, sin nombrar a las personas morales como sujetos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>i01d</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Comunidades, pueblos o colectivos sin personalidad jurídica, nombrados expresamente</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 1, 6 num. 5</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Grupos y comunidades como población objeto; miembros de grupos étnicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>i01e</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    No exige registro, acreditación ni pertenencia a organización</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 2 num. 2, 3 num. 1 y 5</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Exige certificación de la organización o de una autoridad y demostrar la conexidad entre riesgo y actividad</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>i01f</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Reconoce la defensa como actividad ocasional o no profesional</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Art. 3 num. 1</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Exige intervenir 'activamente' y estar acreditado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>i02</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2. Definición amplia e inclusiva de persona periodista</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Art. 6 num. 8</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Nombra a 'periodistas y comunicadores sociales' como población objeto sin definirlos</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>i02a</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Personas físicas, además de medios</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Sin definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>i02b</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Medios de toda índole (públicos, comunitarios, privados, independientes, universitarios, experimentales u otros)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Sin definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>i02c</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Criterio funcional: se es periodista por la actividad de informar, no por título, credencial o relación laboral</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 1, 2 num. 2</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>El vínculo entre riesgo y actividad es el criterio general de ingreso</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>i02d</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    No exige acreditación ni personalidad jurídica</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 2 num. 2, 6 num. 8</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>No exige acreditación a periodistas, pero sí demostrar la conexidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>i02e</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Nombra expresamente a colaboradores, columnistas o auxiliares</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Art. 6 num. 8</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Comunicadores sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>i02f</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Incluye medios y entornos digitales</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>i02g</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Define el periodismo como actividad de interés público, además de definir al periodista</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>i03</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>3. Concepto amplio y adecuado de agresión</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 1, 3 num. 3, 11, 15 a 18</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>No define la agresión: define amenaza y riesgo (ordinario, extraordinario y extremo, con ocho características exigidas al extraordinario) y protege la vida, la libertad, la integridad y la seguridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>i03a</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Vida</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Art. 1</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>i03b</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Integridad física</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Art. 1</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>'Integridad' sin desglose</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>i03c</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Integridad psicológica</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 1, 11 par. 2</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Integridad sin desglose; medidas psicosociales posibles</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>i03d</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Integridad moral</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>i03e</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Integridad económica</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>i03f</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Libertad y seguridad</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Art. 1</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>i03g</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Bienes</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Art. 11 lit. g</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Blindaje de inmuebles</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>i03h</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Derechos</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>i03i</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Entorno familiar, laboral u organizativo</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Art. 3 num. 11</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Núcleo familiar solo de manera excepcional y con riesgo propio</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>i03j</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ámbito digital (campañas, ataques informáticos, revelación de datos)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>i03k</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Acoso judicial (citatorios, demandas para hostigar)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>i03l</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Violencia y acoso sexual</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>i04</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>4. Perspectiva de género y enfoques diferenciados</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 2 num. 8, 9, 10, 11 par. 2, 50</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Enfoque diferencial por edad, etnia, género, discapacidad, orientación sexual y procedencia urbana o rural, exigido en la evaluación del riesgo y en las medidas; la protección específica de lideresas se desarrolló después por el Decreto 1314 de 2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>i05</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>5. Enfoque individual y colectivo de la protección</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 1, 10, 11 tipo 5</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Personas, grupos y comunidades; esquemas colectivos; planes de prevención territoriales. La ruta de protección colectiva se desarrolló por el Decreto 2078 de 2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>i06</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>6. Medidas diversas de protección</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 9, 10, 11</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Medidas de emergencia sin evaluación previa, de prevención (planes de prevención y contingencia, autoprotección, patrullaje) y de protección (esquemas, movilización, reubicación temporal, trasteo, comunicaciones, blindaje), más medidas psicosociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>i06a</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Medidas urgentes de protección</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Art. 9</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>i06b</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Medidas preventivas</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Art. 10</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>i06c</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Medidas de protección</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Art. 11</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>i06d</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Medidas de prevención (política pública)</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 12 a 24</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>i06e</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Medidas de carácter social (atención, apoyo económico, psicológico, retorno)</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Art. 11 lit. d y e, par. 2</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Apoyo económico de reubicación temporal, trasteo y medidas psicosociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>i07</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>7. Participación de sociedad civil, periodistas y personas defensoras con voz y voto en un Consejo Consultivo</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Art. 37</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>No hay consejo consultivo; cuatro delegados de cada población objeto asisten al Cerrem con voz y sin voto, solo en los casos de su grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>i08</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>8. Junta de Gobierno o Consejo de Medidas interinstitucional con instituciones clave</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 34, 36, 37</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Cerrem con Mininterior (preside), Programa Presidencial de DDHH, Unidad de Víctimas y Policía; Fiscalía, Procuraduría, Defensoría, ONU Derechos Humanos y ACNUR como invitados; Grupo de Valoración Preliminar interinstitucional</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>i09</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>9. Obligación legal de cooperación de autoridades locales y cuerpos de seguridad</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 2 num. 4, 6 par. 4, 20, 21, 31, 32</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Asigna atribuciones a gobernaciones, alcaldías, Fuerza Pública y órganos de control, y obliga a todos los servidores a reportar riesgos, sin consecuencia por incumplimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>i10</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>10. Pasos definidos para acceder al mecanismo</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 9, 40, 41, 42</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Once pasos del procedimiento ordinario, medidas de emergencia, presunción constitucional de riesgo para desplazados y reclamantes de tierras y ruta territorial desde la alcaldía</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>i11</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>11. Áreas técnicas diferenciadas (análisis de riesgo, implementación, prevención, monitoreo y seguimiento)</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 28, 29, 33 a 38</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>UNP (recepción e implementación), Ctrai (recopilación in situ), Grupo de Valoración Preliminar (evaluación), Cerrem (recomendación) y Policía (mapas de riesgo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>i12</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>12. Tiempos establecidos para cada procedimiento</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 35, 38, 40 par. 2, 45</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>30 días hábiles para la evaluación del riesgo, Cerrem mensual, reevaluación anual y 5 días para controvertir una suspensión; sin plazo para implementar medidas de emergencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>i13</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>13. Sistemas de alerta temprana y planes de contingencia</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 10, 13, 19, 22, 29</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Planes de prevención y de contingencia, mesas territoriales que proyectan escenarios de riesgo, Sistema de Alertas Tempranas de la Defensoría y mapas de riesgo policiales semestrales</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>i14</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>14. Recursos de inconformidad</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Art. 45</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Sin recurso de inconformidad propio; solo el derecho a controvertir la suspensión por uso indebido. Las decisiones son actos administrativos sujetos a los recursos generales</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>i15</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>15. Posibilidad de firmar convenios de colaboración</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Art. 49</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>i16</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>16. Mesa de trabajo multisectorial</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Art. 13</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Mesa territorial de prevención en cada entidad territorial, coordinada por el gobierno local, con espacios de trabajo entre autoridades y comunidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>i17</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>17. Mecanismos para obtener recursos financieros (fondo, fideicomiso, presupuesto garantizado)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 2 num. 4, 9, 32</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Concurrencia presupuestal de todos los niveles y gasto social prioritario de las alcaldías; sin fondo ni monto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>i18</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>18. Responsabilidades o sanciones para servidores públicos</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>No prevé sanciones a servidores; solo la suspensión de medidas por uso indebido del protegido</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>i19</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>19. Obligación de emitir informes periódicos públicos</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 20, 21, 28, 50</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Rendición de cuentas territorial, seguimiento de la UNP y evaluación periódica del Programa, sin informes públicos obligatorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>i20</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>20. Unidades y mecanismos claros de transparencia y acceso a la información</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>parcial</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Arts. 2 num. 13, 47</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Solo la reserva legal de la información de solicitantes y protegidos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C12:C61" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Valor no permitido" type="list">
+      <formula1>"si,parcial,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10740,889 +13064,25 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>es_subindicador</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>i01</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>1. Definición amplia e inclusiva de persona defensora</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>i01a</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Personas físicas que actúan individualmente</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>i01b</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Integrantes de grupos, organizaciones o movimientos sociales</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>i01c</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Personas morales y organizaciones como sujetos protegidos</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>i01d</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Comunidades, pueblos o colectivos sin personalidad jurídica, nombrados expresamente</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>i01e</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>No exige registro, acreditación ni pertenencia a organización</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>i01f</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Reconoce la defensa como actividad ocasional o no profesional</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>i02</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>2. Definición amplia e inclusiva de persona periodista</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>i02a</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Personas físicas, además de medios</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>i02b</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Medios de toda índole (públicos, comunitarios, privados, independientes, universitarios, experimentales u otros)</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>i02c</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Criterio funcional: se es periodista por la actividad de informar, no por título, credencial o relación laboral</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>i02d</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>No exige acreditación ni personalidad jurídica</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>i02e</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Nombra expresamente a colaboradores, columnistas o auxiliares</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>i02f</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Incluye medios y entornos digitales</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>i02g</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Define el periodismo como actividad de interés público, además de definir al periodista</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>i03</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>3. Concepto amplio y adecuado de agresión</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>i03a</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Vida</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>i03b</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Integridad física</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>i03c</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Integridad psicológica</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>i03d</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Integridad moral</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>i03e</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Integridad económica</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>i03f</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Libertad y seguridad</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>i03g</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Bienes</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>i03h</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Derechos</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>i03i</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Entorno familiar, laboral u organizativo</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>i03j</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Ámbito digital (campañas, ataques informáticos, revelación de datos)</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>i03k</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Acoso judicial (citatorios, demandas para hostigar)</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>i03l</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Violencia y acoso sexual</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>i04</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>4. Perspectiva de género y enfoques diferenciados</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>i05</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>5. Enfoque individual y colectivo de la protección</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>i06</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>6. Medidas diversas de protección</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>i06a</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Medidas urgentes de protección</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>i06b</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Medidas preventivas</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>i06c</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Medidas de protección</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>i06d</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Medidas de prevención (política pública)</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>i06e</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Medidas de carácter social (atención, apoyo económico, psicológico, retorno)</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>i07</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>7. Participación de sociedad civil, periodistas y personas defensoras con voz y voto en un Consejo Consultivo</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>i08</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>8. Junta de Gobierno o Consejo de Medidas interinstitucional con instituciones clave</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>i09</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>9. Obligación legal de cooperación de autoridades locales y cuerpos de seguridad</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>i10</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>10. Pasos definidos para acceder al mecanismo</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>i11</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>11. Áreas técnicas diferenciadas (análisis de riesgo, implementación, prevención, monitoreo y seguimiento)</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>i12</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>12. Tiempos establecidos para cada procedimiento</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>i13</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>13. Sistemas de alerta temprana y planes de contingencia</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>i14</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>14. Recursos de inconformidad</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>i15</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>15. Posibilidad de firmar convenios de colaboración</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>i16</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>16. Mesa de trabajo multisectorial</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>i17</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>17. Mecanismos para obtener recursos financieros (fondo, fideicomiso, presupuesto garantizado)</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>i18</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>18. Responsabilidades o sanciones para servidores públicos</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>i19</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>19. Obligación de emitir informes periódicos públicos</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>i20</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>20. Unidades y mecanismos claros de transparencia y acceso a la información</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>No lo define; el artículo 6, numeral 8, incluye a 'periodistas y comunicadores sociales' entre la población objeto de protección en razón del riesgo.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Activista: Persona que interviene activamente en la defensa de los derechos humanos. La acreditación de una persona como activista, se efectuará mediante certificación que expida por la respectiva organización o grupo al que pertenece o por una autoridad legalmente reconocida. (Art. 3 num. 1) Son objeto de protección los 'dirigentes, representantes o activistas de organizaciones defensoras de derechos humanos, de víctimas, sociales, cívicas, comunales o campesinas' (Art. 6 num. 2).</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>No la define. Amenaza: Factor del riesgo que comprende las situaciones o hechos externos con la potencialidad de causar daño a una persona, grupo o comunidad, a través de una acción intencionada y por cualquier medio. (Art. 3 num. 3) El ingreso depende de un riesgo extraordinario o extremo, que debe ser específico, concreto, presente, importante, serio, claro, excepcional y desproporcionado (Art. 3 num. 15 a 18).</t>
         </is>
       </c>
     </row>

--- a/plantillas/comparativo_marco_legal.xlsx
+++ b/plantillas/comparativo_marco_legal.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Federal</t>
+          <t>México (Ley Federal)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
